--- a/KEY199MECDAT0005_AA_updated.xlsx
+++ b/KEY199MECDAT0005_AA_updated.xlsx
@@ -3827,7 +3827,7 @@
     <row r="75"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageMargins left="1.02" right="0.31496062992126" top="0.551181102362205" bottom="0.118110236220472" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" scale="72"/>
 </worksheet>
 </file>
@@ -4125,10 +4125,7 @@
       <c r="AT6" s="77" t="n"/>
       <c r="AU6" s="77" t="n"/>
       <c r="AV6" s="131" t="n"/>
-      <c r="AW6" s="131">
-        <f>'T-05-06_SH1'!AV6</f>
-        <v/>
-      </c>
+      <c r="AW6" s="131" t="n"/>
       <c r="AX6" s="77" t="n"/>
       <c r="AY6" s="77" t="n"/>
       <c r="AZ6" s="77" t="n"/>
@@ -4256,10 +4253,7 @@
       <c r="I8" s="77" t="n"/>
       <c r="J8" s="77" t="n"/>
       <c r="K8" s="77" t="n"/>
-      <c r="L8" s="77">
-        <f>'T-05-06_SH1'!L8</f>
-        <v/>
-      </c>
+      <c r="L8" s="77" t="n"/>
       <c r="M8" s="77" t="n"/>
       <c r="N8" s="77" t="n"/>
       <c r="O8" s="77" t="n"/>
@@ -4489,10 +4483,7 @@
         </is>
       </c>
       <c r="AN11" s="141" t="n"/>
-      <c r="AO11" s="98">
-        <f>'T-05-06_SH1'!AR11</f>
-        <v/>
-      </c>
+      <c r="AO11" s="98" t="n"/>
       <c r="AP11" s="142" t="n"/>
       <c r="AQ11" s="142" t="n"/>
       <c r="AR11" s="142" t="n"/>
@@ -6682,7 +6673,7 @@
     <row r="75"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0.3149606299212598" footer="0.3149606299212598"/>
+  <pageMargins left="0.314" right="0.31496062992126" top="0.590551181102362" bottom="0.118110236220472" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="77"/>
 </worksheet>
 </file>